--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872777</v>
+        <v>122872845</v>
       </c>
       <c r="B2" t="n">
-        <v>97312</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R2" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872742</v>
+        <v>122872777</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>97312</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,38 +1029,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579364</v>
+        <v>579432</v>
       </c>
       <c r="R5" t="n">
-        <v>6436823</v>
+        <v>6436782</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872845</v>
+        <v>122872759</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,35 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579485</v>
+        <v>579361</v>
       </c>
       <c r="R6" t="n">
-        <v>6436757</v>
+        <v>6436819</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872759</v>
+        <v>122872742</v>
       </c>
       <c r="B7" t="n">
         <v>90964</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579361</v>
+        <v>579364</v>
       </c>
       <c r="R7" t="n">
-        <v>6436819</v>
+        <v>6436823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872845</v>
+        <v>122872759</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579485</v>
+        <v>579361</v>
       </c>
       <c r="R2" t="n">
-        <v>6436757</v>
+        <v>6436819</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872784</v>
+        <v>122872845</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R3" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872804</v>
+        <v>122872777</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>97314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579481</v>
+        <v>579432</v>
       </c>
       <c r="R4" t="n">
-        <v>6436840</v>
+        <v>6436782</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872777</v>
+        <v>122872784</v>
       </c>
       <c r="B5" t="n">
-        <v>97312</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,27 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872759</v>
+        <v>122872804</v>
       </c>
       <c r="B6" t="n">
         <v>90964</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579361</v>
+        <v>579481</v>
       </c>
       <c r="R6" t="n">
-        <v>6436819</v>
+        <v>6436840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872759</v>
+        <v>122872742</v>
       </c>
       <c r="B2" t="n">
         <v>90964</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579361</v>
+        <v>579364</v>
       </c>
       <c r="R2" t="n">
-        <v>6436819</v>
+        <v>6436823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872845</v>
+        <v>122872804</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,13 +827,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579485</v>
+        <v>579481</v>
       </c>
       <c r="R3" t="n">
-        <v>6436757</v>
+        <v>6436840</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872777</v>
+        <v>122872845</v>
       </c>
       <c r="B4" t="n">
-        <v>97314</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +915,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R4" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872784</v>
+        <v>122872777</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>97314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,34 +1033,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872804</v>
+        <v>122872784</v>
       </c>
       <c r="B6" t="n">
-        <v>90964</v>
+        <v>92225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1136,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579481</v>
+        <v>579432</v>
       </c>
       <c r="R6" t="n">
-        <v>6436840</v>
+        <v>6436782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872742</v>
+        <v>122872759</v>
       </c>
       <c r="B7" t="n">
         <v>90964</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579364</v>
+        <v>579361</v>
       </c>
       <c r="R7" t="n">
-        <v>6436823</v>
+        <v>6436819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872777</v>
+        <v>122872784</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,27 +1033,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1124,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872784</v>
+        <v>122872777</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
+        <v>97314</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,34 +1147,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122872742</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872804</v>
+        <v>122872784</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579481</v>
+        <v>579432</v>
       </c>
       <c r="R3" t="n">
-        <v>6436840</v>
+        <v>6436782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872845</v>
+        <v>122872759</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,35 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579485</v>
+        <v>579361</v>
       </c>
       <c r="R4" t="n">
-        <v>6436757</v>
+        <v>6436819</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872784</v>
+        <v>122872777</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>97322</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,34 +1033,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1131,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872777</v>
+        <v>122872845</v>
       </c>
       <c r="B6" t="n">
-        <v>97314</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,31 +1136,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R6" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872759</v>
+        <v>122872804</v>
       </c>
       <c r="B7" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579361</v>
+        <v>579481</v>
       </c>
       <c r="R7" t="n">
-        <v>6436819</v>
+        <v>6436840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872742</v>
+        <v>122872845</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579364</v>
+        <v>579485</v>
       </c>
       <c r="R2" t="n">
-        <v>6436823</v>
+        <v>6436757</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872845</v>
+        <v>122872742</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,13 +1162,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579485</v>
+        <v>579364</v>
       </c>
       <c r="R6" t="n">
-        <v>6436757</v>
+        <v>6436823</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872845</v>
+        <v>122872742</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579485</v>
+        <v>579364</v>
       </c>
       <c r="R2" t="n">
-        <v>6436757</v>
+        <v>6436823</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872784</v>
+        <v>122872777</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>97322</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,34 +805,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -903,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872759</v>
+        <v>122872804</v>
       </c>
       <c r="B4" t="n">
         <v>90972</v>
@@ -938,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579361</v>
+        <v>579481</v>
       </c>
       <c r="R4" t="n">
-        <v>6436819</v>
+        <v>6436840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872777</v>
+        <v>122872845</v>
       </c>
       <c r="B5" t="n">
-        <v>97322</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,31 +1022,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R5" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872742</v>
+        <v>122872759</v>
       </c>
       <c r="B6" t="n">
         <v>90972</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579364</v>
+        <v>579361</v>
       </c>
       <c r="R6" t="n">
-        <v>6436823</v>
+        <v>6436819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872804</v>
+        <v>122872784</v>
       </c>
       <c r="B7" t="n">
-        <v>90972</v>
+        <v>92233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,30 +1250,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579481</v>
+        <v>579432</v>
       </c>
       <c r="R7" t="n">
-        <v>6436840</v>
+        <v>6436782</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872742</v>
+        <v>122872777</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579364</v>
+        <v>579432</v>
       </c>
       <c r="R2" t="n">
-        <v>6436823</v>
+        <v>6436782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872777</v>
+        <v>122872845</v>
       </c>
       <c r="B3" t="n">
-        <v>97322</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +794,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R3" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872804</v>
+        <v>122872742</v>
       </c>
       <c r="B4" t="n">
         <v>90972</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579481</v>
+        <v>579364</v>
       </c>
       <c r="R4" t="n">
-        <v>6436840</v>
+        <v>6436823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872845</v>
+        <v>122872759</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,35 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579485</v>
+        <v>579361</v>
       </c>
       <c r="R5" t="n">
-        <v>6436757</v>
+        <v>6436819</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,6 +1105,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872759</v>
+        <v>122872804</v>
       </c>
       <c r="B6" t="n">
         <v>90972</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579361</v>
+        <v>579481</v>
       </c>
       <c r="R6" t="n">
-        <v>6436819</v>
+        <v>6436840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122872777</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>97325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872845</v>
+        <v>122872804</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,13 +820,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579485</v>
+        <v>579481</v>
       </c>
       <c r="R3" t="n">
-        <v>6436757</v>
+        <v>6436840</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872742</v>
+        <v>122872759</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579364</v>
+        <v>579361</v>
       </c>
       <c r="R4" t="n">
-        <v>6436823</v>
+        <v>6436819</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872759</v>
+        <v>122872845</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,34 +1026,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579361</v>
+        <v>579485</v>
       </c>
       <c r="R5" t="n">
-        <v>6436819</v>
+        <v>6436757</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872804</v>
+        <v>122872742</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579481</v>
+        <v>579364</v>
       </c>
       <c r="R6" t="n">
-        <v>6436840</v>
+        <v>6436823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,7 +1241,7 @@
         <v>122872784</v>
       </c>
       <c r="B7" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872777</v>
+        <v>122872845</v>
       </c>
       <c r="B2" t="n">
-        <v>97325</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579432</v>
+        <v>579485</v>
       </c>
       <c r="R2" t="n">
-        <v>6436782</v>
+        <v>6436757</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872804</v>
+        <v>122872742</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579481</v>
+        <v>579364</v>
       </c>
       <c r="R3" t="n">
-        <v>6436840</v>
+        <v>6436823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +906,7 @@
         <v>122872759</v>
       </c>
       <c r="B4" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1010,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872845</v>
+        <v>122872784</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>92238</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,39 +1029,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579485</v>
+        <v>579432</v>
       </c>
       <c r="R5" t="n">
-        <v>6436757</v>
+        <v>6436782</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872742</v>
+        <v>122872804</v>
       </c>
       <c r="B6" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579364</v>
+        <v>579481</v>
       </c>
       <c r="R6" t="n">
-        <v>6436823</v>
+        <v>6436840</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872784</v>
+        <v>122872777</v>
       </c>
       <c r="B7" t="n">
-        <v>92236</v>
+        <v>97327</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,34 +1261,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,6 +1350,121 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123505878</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90983</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 8284, Kasinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579364</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6436830</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 olika tallar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872742</v>
+        <v>122872804</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579364</v>
+        <v>579481</v>
       </c>
       <c r="R3" t="n">
-        <v>6436823</v>
+        <v>6436840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872759</v>
+        <v>122872777</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>97333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579361</v>
+        <v>579432</v>
       </c>
       <c r="R4" t="n">
-        <v>6436819</v>
+        <v>6436782</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122872784</v>
+        <v>122872759</v>
       </c>
       <c r="B5" t="n">
-        <v>92238</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,30 +1022,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579432</v>
+        <v>579361</v>
       </c>
       <c r="R5" t="n">
-        <v>6436782</v>
+        <v>6436819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872804</v>
+        <v>122872742</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579481</v>
+        <v>579364</v>
       </c>
       <c r="R6" t="n">
-        <v>6436840</v>
+        <v>6436823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872777</v>
+        <v>122872784</v>
       </c>
       <c r="B7" t="n">
-        <v>97327</v>
+        <v>92244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,27 +1254,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122872845</v>
+        <v>122872784</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>92247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579485</v>
+        <v>579432</v>
       </c>
       <c r="R2" t="n">
-        <v>6436757</v>
+        <v>6436782</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122872804</v>
+        <v>122872777</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>97336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579481</v>
+        <v>579432</v>
       </c>
       <c r="R3" t="n">
-        <v>6436840</v>
+        <v>6436782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122872777</v>
+        <v>122872742</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>90986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +908,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579432</v>
+        <v>579364</v>
       </c>
       <c r="R4" t="n">
-        <v>6436782</v>
+        <v>6436823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
         <v>122872759</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122872742</v>
+        <v>122872845</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,12 +1162,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579364</v>
+        <v>579485</v>
       </c>
       <c r="R6" t="n">
-        <v>6436823</v>
+        <v>6436757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122872784</v>
+        <v>122872804</v>
       </c>
       <c r="B7" t="n">
-        <v>92244</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,30 +1250,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579432</v>
+        <v>579481</v>
       </c>
       <c r="R7" t="n">
-        <v>6436782</v>
+        <v>6436840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>123505878</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>90986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>123505878</v>
       </c>
       <c r="B8" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>123505878</v>
       </c>
       <c r="B8" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8284-2025 artfynd.xlsx
+++ b/artfynd/A 8284-2025 artfynd.xlsx
@@ -1355,7 +1355,7 @@
         <v>123505878</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
